--- a/docs/Python 应用开发基础 评分表.xlsx
+++ b/docs/Python 应用开发基础 评分表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kmg/Documents/vscode/Python 课程设计/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kmg/Documents/vscode/Python 课程设计/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C0D7A3-F4BB-9847-98BB-12F4CDC1FF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D0E9C25-CAEB-434B-B197-1B7A6769BCEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26600" yWindow="6820" windowWidth="27880" windowHeight="20300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4300" yWindow="780" windowWidth="29900" windowHeight="21460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="课程设计组间打分" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>第11组</t>
   </si>
@@ -189,10 +189,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>打分组：24（填写一下自己的组号，每组提交一份打分）</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>共享单车算法设计</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -250,6 +246,62 @@
   </si>
   <si>
     <t>《崩坏：星穹铁道》自动配队算法</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>英文社交媒体文本抑郁倾向检测</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>人脸情绪分类</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>电影评分预测</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>自然光光谱预测与照明补偿</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>b 站爆款视频预测</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>知识追踪</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>高分辨率高光谱图像融合</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>YOLO 手势识别</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>二手车价格分析与预测</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>语言模型个性化</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>个人音乐推荐系统</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>b 站热度识别</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>打分组：24</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>神经网络衣物识别</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -791,7 +843,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="8" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="B1" s="12"/>
     </row>
@@ -828,32 +880,60 @@
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
+      <c r="B3" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="5">
+        <v>5</v>
+      </c>
+      <c r="D3" s="5">
+        <v>9</v>
+      </c>
+      <c r="E3" s="5">
+        <v>27</v>
+      </c>
+      <c r="F3" s="5">
+        <v>24</v>
+      </c>
+      <c r="G3" s="5">
+        <v>10</v>
+      </c>
+      <c r="H3" s="5">
+        <v>16</v>
+      </c>
       <c r="I3" s="13">
         <f>SUM(C3:H3)</f>
-        <v>0</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
+      <c r="B4" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="5">
+        <v>5</v>
+      </c>
+      <c r="D4" s="5">
+        <v>8</v>
+      </c>
+      <c r="E4" s="5">
+        <v>27</v>
+      </c>
+      <c r="F4" s="5">
+        <v>23</v>
+      </c>
+      <c r="G4" s="5">
+        <v>8</v>
+      </c>
+      <c r="H4" s="5">
+        <v>18</v>
+      </c>
       <c r="I4" s="13">
         <f t="shared" ref="I4:I32" si="0">SUM(C4:H4)</f>
-        <v>0</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -861,7 +941,7 @@
         <v>16</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" s="5">
         <v>5</v>
@@ -890,7 +970,9 @@
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="10"/>
+      <c r="B6" s="10" t="s">
+        <v>56</v>
+      </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
@@ -907,7 +989,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C7" s="5">
         <v>5</v>
@@ -937,7 +1019,7 @@
         <v>17</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C8" s="5">
         <v>3</v>
@@ -966,48 +1048,90 @@
       <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
+      <c r="B9" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="5">
+        <v>5</v>
+      </c>
+      <c r="D9" s="5">
+        <v>8</v>
+      </c>
+      <c r="E9" s="5">
+        <v>27</v>
+      </c>
+      <c r="F9" s="5">
+        <v>23</v>
+      </c>
+      <c r="G9" s="5">
+        <v>10</v>
+      </c>
+      <c r="H9" s="5">
+        <v>17</v>
+      </c>
       <c r="I9" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
+      <c r="B10" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="5">
+        <v>5</v>
+      </c>
+      <c r="D10" s="5">
+        <v>10</v>
+      </c>
+      <c r="E10" s="5">
+        <v>27</v>
+      </c>
+      <c r="F10" s="5">
+        <v>25</v>
+      </c>
+      <c r="G10" s="5">
+        <v>8</v>
+      </c>
+      <c r="H10" s="5">
+        <v>19</v>
+      </c>
       <c r="I10" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
+      <c r="B11" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="5">
+        <v>5</v>
+      </c>
+      <c r="D11" s="5">
+        <v>8</v>
+      </c>
+      <c r="E11" s="5">
+        <v>26</v>
+      </c>
+      <c r="F11" s="5">
+        <v>22</v>
+      </c>
+      <c r="G11" s="5">
+        <v>8</v>
+      </c>
+      <c r="H11" s="5">
+        <v>17</v>
+      </c>
       <c r="I11" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1015,7 +1139,7 @@
         <v>3</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" s="5">
         <v>5</v>
@@ -1045,7 +1169,7 @@
         <v>0</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5">
@@ -1071,7 +1195,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C14" s="5">
         <v>5</v>
@@ -1100,16 +1224,30 @@
       <c r="A15" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
+      <c r="B15" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="5">
+        <v>5</v>
+      </c>
+      <c r="D15" s="5">
+        <v>7</v>
+      </c>
+      <c r="E15" s="5">
+        <v>22</v>
+      </c>
+      <c r="F15" s="5">
+        <v>21</v>
+      </c>
+      <c r="G15" s="5">
+        <v>8</v>
+      </c>
+      <c r="H15" s="5">
+        <v>16</v>
+      </c>
       <c r="I15" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1117,7 +1255,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" s="2">
         <v>4</v>
@@ -1161,7 +1299,9 @@
       <c r="A18" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="10"/>
+      <c r="B18" s="10" t="s">
+        <v>57</v>
+      </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -1178,7 +1318,7 @@
         <v>7</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C19" s="2">
         <v>5</v>
@@ -1187,7 +1327,7 @@
         <v>8</v>
       </c>
       <c r="E19" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F19" s="2">
         <v>24</v>
@@ -1200,23 +1340,37 @@
       </c>
       <c r="I19" s="13">
         <f t="shared" si="0"/>
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
+      <c r="B20" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="2">
+        <v>4</v>
+      </c>
+      <c r="D20" s="2">
+        <v>9</v>
+      </c>
+      <c r="E20" s="2">
+        <v>26</v>
+      </c>
+      <c r="F20" s="2">
+        <v>22</v>
+      </c>
+      <c r="G20" s="2">
+        <v>9</v>
+      </c>
+      <c r="H20" s="2">
+        <v>19</v>
+      </c>
       <c r="I20" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1224,7 +1378,7 @@
         <v>5</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C21" s="2">
         <v>5</v>
@@ -1253,32 +1407,60 @@
       <c r="A22" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
+      <c r="B22" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="2">
+        <v>5</v>
+      </c>
+      <c r="D22" s="2">
+        <v>9</v>
+      </c>
+      <c r="E22" s="2">
+        <v>26</v>
+      </c>
+      <c r="F22" s="2">
+        <v>23</v>
+      </c>
+      <c r="G22" s="2">
+        <v>10</v>
+      </c>
+      <c r="H22" s="2">
+        <v>18</v>
+      </c>
       <c r="I22" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
+      <c r="B23" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" s="2">
+        <v>5</v>
+      </c>
+      <c r="D23" s="2">
+        <v>9</v>
+      </c>
+      <c r="E23" s="2">
+        <v>25</v>
+      </c>
+      <c r="F23" s="2">
+        <v>22</v>
+      </c>
+      <c r="G23" s="2">
+        <v>8</v>
+      </c>
+      <c r="H23" s="2">
+        <v>16</v>
+      </c>
       <c r="I23" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1286,7 +1468,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C24" s="2">
         <v>5</v>
@@ -1316,7 +1498,7 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C25">
         <v>4</v>
@@ -1345,6 +1527,9 @@
       <c r="A26" s="4" t="s">
         <v>32</v>
       </c>
+      <c r="B26" s="10" t="s">
+        <v>58</v>
+      </c>
       <c r="C26">
         <v>0</v>
       </c>
@@ -1372,9 +1557,30 @@
       <c r="A27" s="4" t="s">
         <v>33</v>
       </c>
+      <c r="B27" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="2">
+        <v>4</v>
+      </c>
+      <c r="D27" s="2">
+        <v>10</v>
+      </c>
+      <c r="E27" s="2">
+        <v>25</v>
+      </c>
+      <c r="F27" s="2">
+        <v>24</v>
+      </c>
+      <c r="G27" s="2">
+        <v>7</v>
+      </c>
+      <c r="H27" s="2">
+        <v>17</v>
+      </c>
       <c r="I27" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1382,7 +1588,7 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C28">
         <v>3</v>
@@ -1412,7 +1618,7 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C29">
         <v>5</v>
@@ -1442,7 +1648,7 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C30">
         <v>4</v>
@@ -1472,7 +1678,7 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C31">
         <v>3</v>
